--- a/backend/data/financials_by_company/0JX.F.xlsx
+++ b/backend/data/financials_by_company/0JX.F.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,616 +677,675 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-1526511</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.2778</v>
-      </c>
-      <c r="D2" t="n">
-        <v>475973000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-5495000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-5495000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>261939000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>71092000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>470478000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>399386000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1868000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>17367000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>19235000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>265907489</v>
-      </c>
-      <c r="O2" t="n">
-        <v>261939000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1238896000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>16589000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>858195000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>846551000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="V2" t="n">
-        <v>261939000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>261939000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>261939000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-13943000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>275882000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>275882000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>106137000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>382019000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>12877000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-5474000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-1526000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1868000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>17367000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>19235000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>372769000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1238896000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>273835000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>71092000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9718000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>61374000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>109768000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>97152000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>54055000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>43097000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16589000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1611665000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1611665000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>29969000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>39268.8</v>
+        <v>-2098419</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2727</v>
+        <v>0.309</v>
       </c>
       <c r="D3" t="n">
-        <v>411036000</v>
+        <v>363510000</v>
       </c>
       <c r="E3" t="n">
-        <v>144000</v>
+        <v>-6791000</v>
       </c>
       <c r="F3" t="n">
-        <v>144000</v>
+        <v>-6791000</v>
       </c>
       <c r="G3" t="n">
-        <v>208247000</v>
+        <v>165638000</v>
       </c>
       <c r="H3" t="n">
-        <v>70474000</v>
+        <v>68353000</v>
       </c>
       <c r="I3" t="n">
-        <v>411180000</v>
+        <v>356719000</v>
       </c>
       <c r="J3" t="n">
-        <v>340706000</v>
+        <v>288366000</v>
       </c>
       <c r="K3" t="n">
-        <v>3963000</v>
+        <v>-6612000</v>
       </c>
       <c r="L3" t="n">
-        <v>16677000</v>
+        <v>18650000</v>
       </c>
       <c r="M3" t="n">
-        <v>20640000</v>
+        <v>12038000</v>
       </c>
       <c r="N3" t="n">
-        <v>208142268.8</v>
+        <v>170330581</v>
       </c>
       <c r="O3" t="n">
-        <v>208247000</v>
+        <v>165638000</v>
       </c>
       <c r="P3" t="n">
-        <v>1108153000</v>
+        <v>935604000</v>
       </c>
       <c r="Q3" t="n">
-        <v>15206000</v>
+        <v>14357000</v>
       </c>
       <c r="R3" t="n">
-        <v>862504000</v>
+        <v>868412000</v>
       </c>
       <c r="S3" t="n">
-        <v>849346000</v>
+        <v>849421000</v>
       </c>
       <c r="T3" t="n">
-        <v>0.241</v>
+        <v>0.191</v>
       </c>
       <c r="U3" t="n">
-        <v>0.245</v>
+        <v>0.195</v>
       </c>
       <c r="V3" t="n">
-        <v>208247000</v>
+        <v>165638000</v>
       </c>
       <c r="W3" t="n">
-        <v>208247000</v>
+        <v>165638000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>208247000</v>
+        <v>165638000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-28015000</v>
+        <v>-20850000</v>
       </c>
       <c r="AA3" t="n">
-        <v>236262000</v>
+        <v>186488000</v>
       </c>
       <c r="AB3" t="n">
-        <v>236262000</v>
+        <v>186488000</v>
       </c>
       <c r="AC3" t="n">
-        <v>87767000</v>
+        <v>83228000</v>
       </c>
       <c r="AD3" t="n">
-        <v>324029000</v>
+        <v>269716000</v>
       </c>
       <c r="AE3" t="n">
-        <v>14425000</v>
+        <v>4911000</v>
       </c>
       <c r="AF3" t="n">
-        <v>165000</v>
+        <v>-6918000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-165000</v>
+        <v>462000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>6456000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>6456000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3963000</v>
+        <v>-6612000</v>
       </c>
       <c r="AK3" t="n">
-        <v>16677000</v>
+        <v>18650000</v>
       </c>
       <c r="AL3" t="n">
-        <v>20640000</v>
+        <v>12038000</v>
       </c>
       <c r="AM3" t="n">
-        <v>305497000</v>
+        <v>278208000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1108153000</v>
+        <v>935604000</v>
       </c>
       <c r="AO3" t="n">
-        <v>241695000</v>
+        <v>173360000</v>
       </c>
       <c r="AP3" t="n">
-        <v>70474000</v>
+        <v>68353000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11631000</v>
+        <v>14921000</v>
       </c>
       <c r="AR3" t="n">
-        <v>58843000</v>
+        <v>53432000</v>
       </c>
       <c r="AS3" t="n">
-        <v>97654000</v>
+        <v>59040000</v>
       </c>
       <c r="AT3" t="n">
-        <v>92508000</v>
+        <v>100742000</v>
       </c>
       <c r="AU3" t="n">
-        <v>54178000</v>
+        <v>42534000</v>
       </c>
       <c r="AV3" t="n">
-        <v>38330000</v>
+        <v>58208000</v>
       </c>
       <c r="AW3" t="n">
-        <v>15206000</v>
+        <v>14357000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1413650000</v>
+        <v>1213812000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1413650000</v>
+        <v>1213812000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-2098419</v>
+        <v>39268.8</v>
       </c>
       <c r="C4" t="n">
-        <v>0.309</v>
+        <v>0.2727</v>
       </c>
       <c r="D4" t="n">
-        <v>363510000</v>
+        <v>411036000</v>
       </c>
       <c r="E4" t="n">
-        <v>-6791000</v>
+        <v>144000</v>
       </c>
       <c r="F4" t="n">
-        <v>-6791000</v>
+        <v>144000</v>
       </c>
       <c r="G4" t="n">
-        <v>165638000</v>
+        <v>208247000</v>
       </c>
       <c r="H4" t="n">
-        <v>68353000</v>
+        <v>70474000</v>
       </c>
       <c r="I4" t="n">
-        <v>356719000</v>
+        <v>411180000</v>
       </c>
       <c r="J4" t="n">
-        <v>288366000</v>
+        <v>340706000</v>
       </c>
       <c r="K4" t="n">
-        <v>-6612000</v>
+        <v>3963000</v>
       </c>
       <c r="L4" t="n">
-        <v>18650000</v>
+        <v>16677000</v>
       </c>
       <c r="M4" t="n">
-        <v>12038000</v>
+        <v>20640000</v>
       </c>
       <c r="N4" t="n">
-        <v>170330581</v>
+        <v>208142268.8</v>
       </c>
       <c r="O4" t="n">
-        <v>165638000</v>
+        <v>208247000</v>
       </c>
       <c r="P4" t="n">
-        <v>935604000</v>
+        <v>1108153000</v>
       </c>
       <c r="Q4" t="n">
-        <v>14357000</v>
+        <v>15206000</v>
       </c>
       <c r="R4" t="n">
-        <v>868412000</v>
+        <v>862504000</v>
       </c>
       <c r="S4" t="n">
-        <v>849421000</v>
+        <v>849346000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.191</v>
+        <v>0.241</v>
       </c>
       <c r="U4" t="n">
-        <v>0.195</v>
+        <v>0.245</v>
       </c>
       <c r="V4" t="n">
-        <v>165638000</v>
+        <v>208247000</v>
       </c>
       <c r="W4" t="n">
-        <v>165638000</v>
+        <v>208247000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>165638000</v>
+        <v>208247000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-20850000</v>
+        <v>-28015000</v>
       </c>
       <c r="AA4" t="n">
-        <v>186488000</v>
+        <v>236262000</v>
       </c>
       <c r="AB4" t="n">
-        <v>186488000</v>
+        <v>236262000</v>
       </c>
       <c r="AC4" t="n">
-        <v>83228000</v>
+        <v>87767000</v>
       </c>
       <c r="AD4" t="n">
-        <v>269716000</v>
+        <v>324029000</v>
       </c>
       <c r="AE4" t="n">
-        <v>4911000</v>
+        <v>14425000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-6918000</v>
+        <v>165000</v>
       </c>
       <c r="AG4" t="n">
-        <v>462000</v>
+        <v>-165000</v>
       </c>
       <c r="AH4" t="n">
-        <v>6456000</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>6456000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-6612000</v>
+        <v>3963000</v>
       </c>
       <c r="AK4" t="n">
-        <v>18650000</v>
+        <v>16677000</v>
       </c>
       <c r="AL4" t="n">
-        <v>12038000</v>
+        <v>20640000</v>
       </c>
       <c r="AM4" t="n">
-        <v>278208000</v>
+        <v>305497000</v>
       </c>
       <c r="AN4" t="n">
-        <v>935604000</v>
+        <v>1108153000</v>
       </c>
       <c r="AO4" t="n">
-        <v>173360000</v>
+        <v>241695000</v>
       </c>
       <c r="AP4" t="n">
-        <v>68353000</v>
+        <v>70474000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14921000</v>
+        <v>11631000</v>
       </c>
       <c r="AR4" t="n">
-        <v>53432000</v>
+        <v>58843000</v>
       </c>
       <c r="AS4" t="n">
-        <v>59040000</v>
+        <v>97654000</v>
       </c>
       <c r="AT4" t="n">
-        <v>100742000</v>
+        <v>92508000</v>
       </c>
       <c r="AU4" t="n">
-        <v>42534000</v>
+        <v>54178000</v>
       </c>
       <c r="AV4" t="n">
-        <v>58208000</v>
+        <v>38330000</v>
       </c>
       <c r="AW4" t="n">
-        <v>14357000</v>
+        <v>15206000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1213812000</v>
+        <v>1413650000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1213812000</v>
+        <v>1413650000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-8917020</v>
+        <v>-1526685.361199</v>
       </c>
       <c r="C5" t="n">
-        <v>0.315</v>
+        <v>0.277832</v>
       </c>
       <c r="D5" t="n">
-        <v>316409000</v>
+        <v>475973000</v>
       </c>
       <c r="E5" t="n">
-        <v>-28308000</v>
+        <v>-5495000</v>
       </c>
       <c r="F5" t="n">
-        <v>-28308000</v>
+        <v>-5495000</v>
       </c>
       <c r="G5" t="n">
-        <v>126005000</v>
+        <v>261939000</v>
       </c>
       <c r="H5" t="n">
-        <v>66707000</v>
+        <v>71092000</v>
       </c>
       <c r="I5" t="n">
-        <v>288101000</v>
+        <v>470478000</v>
       </c>
       <c r="J5" t="n">
-        <v>221394000</v>
+        <v>399386000</v>
       </c>
       <c r="K5" t="n">
-        <v>-12157000</v>
+        <v>1868000</v>
       </c>
       <c r="L5" t="n">
-        <v>20730000</v>
+        <v>17367000</v>
       </c>
       <c r="M5" t="n">
-        <v>8573000</v>
+        <v>19235000</v>
       </c>
       <c r="N5" t="n">
-        <v>145395980</v>
+        <v>265907314.638801</v>
       </c>
       <c r="O5" t="n">
-        <v>126005000</v>
+        <v>261939000</v>
       </c>
       <c r="P5" t="n">
-        <v>863824000</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>1238896000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>16589000</v>
+      </c>
       <c r="R5" t="n">
-        <v>867841000</v>
+        <v>858195000</v>
       </c>
       <c r="S5" t="n">
-        <v>844770000</v>
+        <v>846551000</v>
       </c>
       <c r="T5" t="n">
-        <v>0.145</v>
+        <v>0.305</v>
       </c>
       <c r="U5" t="n">
-        <v>0.149</v>
+        <v>0.309</v>
       </c>
       <c r="V5" t="n">
-        <v>126005000</v>
+        <v>261939000</v>
       </c>
       <c r="W5" t="n">
-        <v>126005000</v>
+        <v>261939000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>126005000</v>
+        <v>261939000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-11435000</v>
+        <v>-13943000</v>
       </c>
       <c r="AA5" t="n">
-        <v>137440000</v>
+        <v>275882000</v>
       </c>
       <c r="AB5" t="n">
-        <v>137440000</v>
+        <v>275882000</v>
       </c>
       <c r="AC5" t="n">
-        <v>63224000</v>
+        <v>106137000</v>
       </c>
       <c r="AD5" t="n">
-        <v>200664000</v>
+        <v>382019000</v>
       </c>
       <c r="AE5" t="n">
-        <v>7185000</v>
+        <v>12877000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-27611000</v>
+        <v>-5474000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-2358000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>29969000</v>
-      </c>
+        <v>-1526000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>29969000</v>
+        <v>7000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-12157000</v>
+        <v>1868000</v>
       </c>
       <c r="AK5" t="n">
-        <v>20730000</v>
+        <v>17367000</v>
       </c>
       <c r="AL5" t="n">
-        <v>8573000</v>
+        <v>19235000</v>
       </c>
       <c r="AM5" t="n">
-        <v>233944000</v>
+        <v>372769000</v>
       </c>
       <c r="AN5" t="n">
-        <v>863824000</v>
+        <v>1238896000</v>
       </c>
       <c r="AO5" t="n">
-        <v>231605000</v>
+        <v>273835000</v>
       </c>
       <c r="AP5" t="n">
-        <v>66707000</v>
+        <v>71092000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16394000</v>
+        <v>9718000</v>
       </c>
       <c r="AR5" t="n">
-        <v>50313000</v>
+        <v>61374000</v>
       </c>
       <c r="AS5" t="n">
-        <v>46919000</v>
+        <v>109768000</v>
       </c>
       <c r="AT5" t="n">
-        <v>40513000</v>
+        <v>97152000</v>
       </c>
       <c r="AU5" t="n">
-        <v>36348000</v>
+        <v>54055000</v>
       </c>
       <c r="AV5" t="n">
-        <v>4165000</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+        <v>43097000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>16589000</v>
+      </c>
       <c r="AX5" t="n">
-        <v>1097768000</v>
+        <v>1611665000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1097768000</v>
+        <v>1611665000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>267824.316427</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.285223</v>
+      </c>
+      <c r="D6" t="n">
+        <v>574696000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>939000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>939000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>327540000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>81676000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>575635000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>493959000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6046000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>16578000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>22624000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>326868824.316427</v>
+      </c>
+      <c r="O6" t="n">
+        <v>327540000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1381753000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>16107000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>862367000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>849292000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="V6" t="n">
+        <v>327540000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>327540000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>327540000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-13681000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>341221000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>341221000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>136160000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>477381000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>11152000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>951000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-491000</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>-460000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>6046000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>16578000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>22624000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>459244000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1381753000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>308974000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>81676000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10344000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>71332000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>135830000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>110583000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>61126000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>49457000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>16107000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1840997000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1840997000</v>
       </c>
     </row>
   </sheetData>
@@ -1300,7 +1359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR5"/>
+  <dimension ref="A1:BR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,315 +1711,211 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>130563</v>
-      </c>
-      <c r="C2" t="n">
-        <v>848169437</v>
-      </c>
-      <c r="D2" t="n">
-        <v>848300000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>112671000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1034285000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1957404000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>159982000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1034285000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>112179000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1956912000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1956912000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2023682000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>66770000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1956912000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>22176000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>790000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>316587000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1618939000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1618939000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>365637000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>145803000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>968000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>64654000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>80181000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>80181000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>219834000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>32490000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>31998000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>492000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>28399000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>24055000</v>
-      </c>
+        <v>28244000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>15628000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1268000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>7159000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2389319000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2009503000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>89614000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>4882000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>4882000</v>
-      </c>
-      <c r="AP2" t="n">
+        <v>41818000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="n">
         <v>0</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="BI2" t="n">
         <v>0</v>
       </c>
-      <c r="AR2" t="n">
-        <v>922627000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>171545000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>751082000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>951367000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-311890000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1263257000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>38378000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>105822000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>132141000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>792978000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>193938000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>379816000</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="n">
-        <v>2255000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="n">
-        <v>39328000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>208294000</v>
-      </c>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="n">
-        <v>129939000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>129939000</v>
-      </c>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="n">
+        <v>25896000</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>39696000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>3710796</v>
+        <v>234757</v>
       </c>
       <c r="C3" t="n">
-        <v>846806204</v>
+        <v>850292243</v>
       </c>
       <c r="D3" t="n">
-        <v>850517000</v>
+        <v>850527000</v>
       </c>
       <c r="E3" t="n">
-        <v>115346000</v>
+        <v>169944000</v>
       </c>
       <c r="F3" t="n">
-        <v>891615000</v>
+        <v>879956000</v>
       </c>
       <c r="G3" t="n">
-        <v>1794902000</v>
+        <v>1772349000</v>
       </c>
       <c r="H3" t="n">
-        <v>41479000</v>
+        <v>90645000</v>
       </c>
       <c r="I3" t="n">
-        <v>891615000</v>
+        <v>879956000</v>
       </c>
       <c r="J3" t="n">
-        <v>115013000</v>
+        <v>169780000</v>
       </c>
       <c r="K3" t="n">
-        <v>1794569000</v>
+        <v>1772185000</v>
       </c>
       <c r="L3" t="n">
-        <v>1794569000</v>
+        <v>1772185000</v>
       </c>
       <c r="M3" t="n">
-        <v>1862202000</v>
+        <v>1881702000</v>
       </c>
       <c r="N3" t="n">
-        <v>67633000</v>
+        <v>109517000</v>
       </c>
       <c r="O3" t="n">
-        <v>1794569000</v>
+        <v>1772185000</v>
       </c>
       <c r="P3" t="n">
-        <v>24361000</v>
+        <v>16960000</v>
       </c>
       <c r="Q3" t="n">
-        <v>17114000</v>
+        <v>145000</v>
       </c>
       <c r="R3" t="n">
-        <v>158541000</v>
+        <v>126853000</v>
       </c>
       <c r="S3" t="n">
-        <v>1628781000</v>
+        <v>1628517000</v>
       </c>
       <c r="T3" t="n">
-        <v>1628781000</v>
+        <v>1628517000</v>
       </c>
       <c r="U3" t="n">
-        <v>453786000</v>
+        <v>399463000</v>
       </c>
       <c r="V3" t="n">
-        <v>132195000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>173451000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2676000</v>
+      </c>
       <c r="X3" t="n">
-        <v>51897000</v>
+        <v>43320000</v>
       </c>
       <c r="Y3" t="n">
-        <v>80298000</v>
+        <v>127455000</v>
       </c>
       <c r="Z3" t="n">
-        <v>80298000</v>
+        <v>127455000</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>321591000</v>
+        <v>226012000</v>
       </c>
       <c r="AC3" t="n">
-        <v>35048000</v>
+        <v>42489000</v>
       </c>
       <c r="AD3" t="n">
-        <v>34715000</v>
+        <v>42325000</v>
       </c>
       <c r="AE3" t="n">
-        <v>333000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>24906000</v>
-      </c>
+        <v>164000</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>143226000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>138671000</v>
-      </c>
+        <v>87253000</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>347000</v>
+        <v>20120000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4208000</v>
+        <v>67133000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2315988000</v>
+        <v>2281165000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1952918000</v>
+        <v>1964508000</v>
       </c>
       <c r="AM3" t="n">
-        <v>75844000</v>
+        <v>86783000</v>
       </c>
       <c r="AN3" t="n">
-        <v>16244000</v>
+        <v>14740000</v>
       </c>
       <c r="AO3" t="n">
-        <v>16244000</v>
+        <v>14740000</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -1969,186 +1924,196 @@
         <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>902954000</v>
+        <v>892229000</v>
       </c>
       <c r="AS3" t="n">
-        <v>151872000</v>
+        <v>141147000</v>
       </c>
       <c r="AT3" t="n">
         <v>751082000</v>
       </c>
       <c r="AU3" t="n">
-        <v>937343000</v>
+        <v>951379000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-182725000</v>
+        <v>-154451000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1120068000</v>
+        <v>1105830000</v>
       </c>
       <c r="AX3" t="n">
-        <v>8604000</v>
+        <v>40085000</v>
       </c>
       <c r="AY3" t="n">
-        <v>60629000</v>
+        <v>53503000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>90527000</v>
+        <v>90249000</v>
       </c>
       <c r="BA3" t="n">
-        <v>763682000</v>
+        <v>726118000</v>
       </c>
       <c r="BB3" t="n">
-        <v>196626000</v>
+        <v>195875000</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>363070000</v>
+        <v>316657000</v>
       </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
         <v>2255000</v>
       </c>
-      <c r="BG3" t="inlineStr"/>
+      <c r="BG3" t="n">
+        <v>19218000</v>
+      </c>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
+      <c r="BJ3" t="n">
+        <v>8855000</v>
+      </c>
       <c r="BK3" t="n">
-        <v>36203000</v>
+        <v>9592000</v>
       </c>
       <c r="BL3" t="n">
-        <v>196544000</v>
-      </c>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
+        <v>158858000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>-132971000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>260412000</v>
+      </c>
       <c r="BO3" t="n">
-        <v>128068000</v>
+        <v>145952000</v>
       </c>
       <c r="BP3" t="n">
-        <v>128068000</v>
+        <v>145952000</v>
       </c>
       <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>234757</v>
+        <v>3710796</v>
       </c>
       <c r="C4" t="n">
-        <v>850292243</v>
+        <v>846806204</v>
       </c>
       <c r="D4" t="n">
-        <v>850527000</v>
+        <v>850517000</v>
       </c>
       <c r="E4" t="n">
-        <v>169944000</v>
+        <v>115346000</v>
       </c>
       <c r="F4" t="n">
-        <v>879956000</v>
+        <v>891615000</v>
       </c>
       <c r="G4" t="n">
-        <v>1772349000</v>
+        <v>1794902000</v>
       </c>
       <c r="H4" t="n">
-        <v>90645000</v>
+        <v>41479000</v>
       </c>
       <c r="I4" t="n">
-        <v>879956000</v>
+        <v>891615000</v>
       </c>
       <c r="J4" t="n">
-        <v>169780000</v>
+        <v>115013000</v>
       </c>
       <c r="K4" t="n">
-        <v>1772185000</v>
+        <v>1794569000</v>
       </c>
       <c r="L4" t="n">
-        <v>1772185000</v>
+        <v>1794569000</v>
       </c>
       <c r="M4" t="n">
-        <v>1881702000</v>
+        <v>1862202000</v>
       </c>
       <c r="N4" t="n">
-        <v>109517000</v>
+        <v>67633000</v>
       </c>
       <c r="O4" t="n">
-        <v>1772185000</v>
+        <v>1794569000</v>
       </c>
       <c r="P4" t="n">
-        <v>16960000</v>
+        <v>24361000</v>
       </c>
       <c r="Q4" t="n">
-        <v>145000</v>
+        <v>17114000</v>
       </c>
       <c r="R4" t="n">
-        <v>126853000</v>
+        <v>158541000</v>
       </c>
       <c r="S4" t="n">
-        <v>1628517000</v>
+        <v>1628781000</v>
       </c>
       <c r="T4" t="n">
-        <v>1628517000</v>
+        <v>1628781000</v>
       </c>
       <c r="U4" t="n">
-        <v>399463000</v>
+        <v>453786000</v>
       </c>
       <c r="V4" t="n">
-        <v>173451000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2676000</v>
-      </c>
+        <v>132195000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>43320000</v>
+        <v>51897000</v>
       </c>
       <c r="Y4" t="n">
-        <v>127455000</v>
+        <v>80298000</v>
       </c>
       <c r="Z4" t="n">
-        <v>127455000</v>
+        <v>80298000</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>226012000</v>
+        <v>321591000</v>
       </c>
       <c r="AC4" t="n">
-        <v>42489000</v>
+        <v>35048000</v>
       </c>
       <c r="AD4" t="n">
-        <v>42325000</v>
+        <v>34715000</v>
       </c>
       <c r="AE4" t="n">
-        <v>164000</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>333000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>24906000</v>
+      </c>
       <c r="AG4" t="n">
-        <v>87253000</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>143226000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>138671000</v>
+      </c>
       <c r="AI4" t="n">
-        <v>20120000</v>
+        <v>347000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>67133000</v>
+        <v>4208000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2281165000</v>
+        <v>2315988000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1964508000</v>
+        <v>1952918000</v>
       </c>
       <c r="AM4" t="n">
-        <v>86783000</v>
+        <v>75844000</v>
       </c>
       <c r="AN4" t="n">
-        <v>14740000</v>
+        <v>16244000</v>
       </c>
       <c r="AO4" t="n">
-        <v>14740000</v>
+        <v>16244000</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -2157,196 +2122,190 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>892229000</v>
+        <v>902954000</v>
       </c>
       <c r="AS4" t="n">
-        <v>141147000</v>
+        <v>151872000</v>
       </c>
       <c r="AT4" t="n">
         <v>751082000</v>
       </c>
       <c r="AU4" t="n">
-        <v>951379000</v>
+        <v>937343000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-154451000</v>
+        <v>-182725000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1105830000</v>
+        <v>1120068000</v>
       </c>
       <c r="AX4" t="n">
-        <v>40085000</v>
+        <v>8604000</v>
       </c>
       <c r="AY4" t="n">
-        <v>53503000</v>
+        <v>60629000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>90249000</v>
+        <v>90527000</v>
       </c>
       <c r="BA4" t="n">
-        <v>726118000</v>
+        <v>763682000</v>
       </c>
       <c r="BB4" t="n">
-        <v>195875000</v>
+        <v>196626000</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>316657000</v>
+        <v>363070000</v>
       </c>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
         <v>2255000</v>
       </c>
-      <c r="BG4" t="n">
-        <v>19218000</v>
-      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="n">
-        <v>8855000</v>
-      </c>
+      <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="n">
-        <v>9592000</v>
+        <v>36203000</v>
       </c>
       <c r="BL4" t="n">
-        <v>158858000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>-132971000</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>260412000</v>
-      </c>
+        <v>196544000</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="n">
-        <v>145952000</v>
+        <v>128068000</v>
       </c>
       <c r="BP4" t="n">
-        <v>145952000</v>
+        <v>128068000</v>
       </c>
       <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>130563</v>
+      </c>
       <c r="C5" t="n">
-        <v>848193000</v>
+        <v>848169437</v>
       </c>
       <c r="D5" t="n">
-        <v>848193000</v>
+        <v>848300000</v>
       </c>
       <c r="E5" t="n">
-        <v>199518000</v>
+        <v>112671000</v>
       </c>
       <c r="F5" t="n">
-        <v>748936000</v>
+        <v>1034285000</v>
       </c>
       <c r="G5" t="n">
-        <v>1667110000</v>
+        <v>1957404000</v>
       </c>
       <c r="H5" t="n">
-        <v>-33486000</v>
+        <v>159982000</v>
       </c>
       <c r="I5" t="n">
-        <v>748936000</v>
+        <v>1034285000</v>
       </c>
       <c r="J5" t="n">
-        <v>184357000</v>
+        <v>112179000</v>
       </c>
       <c r="K5" t="n">
-        <v>1651949000</v>
+        <v>1956912000</v>
       </c>
       <c r="L5" t="n">
-        <v>1651949000</v>
+        <v>1956912000</v>
       </c>
       <c r="M5" t="n">
-        <v>1751177000</v>
+        <v>2023682000</v>
       </c>
       <c r="N5" t="n">
-        <v>99228000</v>
+        <v>66770000</v>
       </c>
       <c r="O5" t="n">
-        <v>1651949000</v>
+        <v>1956912000</v>
       </c>
       <c r="P5" t="n">
-        <v>31942000</v>
+        <v>22176000</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>790000</v>
       </c>
       <c r="R5" t="n">
-        <v>1190000</v>
+        <v>316587000</v>
       </c>
       <c r="S5" t="n">
-        <v>1618817000</v>
+        <v>1618939000</v>
       </c>
       <c r="T5" t="n">
-        <v>1618817000</v>
+        <v>1618939000</v>
       </c>
       <c r="U5" t="n">
-        <v>417468000</v>
+        <v>365637000</v>
       </c>
       <c r="V5" t="n">
-        <v>187968000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>145803000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>968000</v>
+      </c>
       <c r="X5" t="n">
-        <v>39186000</v>
+        <v>64654000</v>
       </c>
       <c r="Y5" t="n">
-        <v>148782000</v>
+        <v>80181000</v>
       </c>
       <c r="Z5" t="n">
-        <v>148782000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
+        <v>80181000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>229500000</v>
+        <v>219834000</v>
       </c>
       <c r="AC5" t="n">
-        <v>50736000</v>
+        <v>32490000</v>
       </c>
       <c r="AD5" t="n">
-        <v>35575000</v>
+        <v>31998000</v>
       </c>
       <c r="AE5" t="n">
-        <v>15161000</v>
+        <v>492000</v>
       </c>
       <c r="AF5" t="n">
-        <v>28244000</v>
+        <v>28399000</v>
       </c>
       <c r="AG5" t="n">
-        <v>101984000</v>
+        <v>24055000</v>
       </c>
       <c r="AH5" t="n">
-        <v>41818000</v>
+        <v>15628000</v>
       </c>
       <c r="AI5" t="n">
-        <v>10911000</v>
+        <v>1268000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>91073000</v>
+        <v>7159000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2168645000</v>
+        <v>2389319000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1972631000</v>
+        <v>2009503000</v>
       </c>
       <c r="AM5" t="n">
-        <v>82639000</v>
+        <v>89614000</v>
       </c>
       <c r="AN5" t="n">
-        <v>9190000</v>
+        <v>4882000</v>
       </c>
       <c r="AO5" t="n">
-        <v>9190000</v>
+        <v>4882000</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2355,78 +2314,258 @@
         <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>903013000</v>
+        <v>922627000</v>
       </c>
       <c r="AS5" t="n">
-        <v>151931000</v>
+        <v>171545000</v>
       </c>
       <c r="AT5" t="n">
         <v>751082000</v>
       </c>
       <c r="AU5" t="n">
-        <v>907504000</v>
+        <v>951367000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-116774000</v>
+        <v>-311890000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1024278000</v>
+        <v>1263257000</v>
       </c>
       <c r="AX5" t="n">
-        <v>29191000</v>
+        <v>38378000</v>
       </c>
       <c r="AY5" t="n">
-        <v>49792000</v>
+        <v>105822000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>77871000</v>
+        <v>132141000</v>
       </c>
       <c r="BA5" t="n">
-        <v>671491000</v>
+        <v>792978000</v>
       </c>
       <c r="BB5" t="n">
-        <v>195933000</v>
+        <v>193938000</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>196014000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>52000000</v>
-      </c>
+        <v>379816000</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
         <v>2255000</v>
       </c>
       <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="inlineStr"/>
       <c r="BK5" t="n">
-        <v>15479000</v>
+        <v>39328000</v>
       </c>
       <c r="BL5" t="n">
-        <v>114943000</v>
+        <v>208294000</v>
       </c>
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="n">
-        <v>63337000</v>
+        <v>129939000</v>
       </c>
       <c r="BP5" t="n">
-        <v>63337000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>25896000</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>39696000</v>
-      </c>
+        <v>129939000</v>
+      </c>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>845786364</v>
+      </c>
+      <c r="D6" t="n">
+        <v>845786364</v>
+      </c>
+      <c r="E6" t="n">
+        <v>251737000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1131020000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2195878000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>53883000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1131020000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>131442000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2075583000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2075583000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2145154000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>69571000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2075583000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>23457000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>474197000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1577929000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1577929000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>529484000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>182077000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1133000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>74559000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>106385000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>106385000</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>347407000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>145352000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>25057000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>120295000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>27075000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>28821000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>14519000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3249000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>11053000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2674638000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2273348000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>101747000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>5033000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>5033000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>944563000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>193481000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>751082000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1198949000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-318121000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1517070000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>153639000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>124230000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>168648000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>876615000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>193938000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>401290000</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>2255000</v>
+      </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="n">
+        <v>17333000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>227981000</v>
+      </c>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="n">
+        <v>153721000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>153721000</v>
+      </c>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2439,7 +2578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2693,621 +2832,688 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Net Other Investing Changes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>249424000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-14949000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-102006000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>102176000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2942000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-106109000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>132194000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>130323000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1871000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-259807000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-123362000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-84674000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-84674000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-12007000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-14949000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2942000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>170000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>102176000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>170000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-102006000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>102176000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-93855000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>11891000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-109000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-29407000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-29407000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-76339000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>363000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-76702000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>355533000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-109622000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>17336000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-17367000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-4910000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>10669000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-3641000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>-11938000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-1992000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11805000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>71092000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9718000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>61374000</v>
-      </c>
+        <v>122065000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>1588000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>-551000</v>
+        <v>-210000</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>723000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>382019000</v>
-      </c>
+        <v>99000</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>186034000</v>
+        <v>137060000</v>
       </c>
       <c r="C3" t="n">
-        <v>-36400000</v>
+        <v>-14862000</v>
       </c>
       <c r="D3" t="n">
-        <v>-52000</v>
+        <v>-15065000</v>
       </c>
       <c r="E3" t="n">
-        <v>221000</v>
+        <v>68000</v>
       </c>
       <c r="F3" t="n">
-        <v>3319000</v>
+        <v>7883000</v>
       </c>
       <c r="G3" t="n">
-        <v>-59692000</v>
+        <v>-92866000</v>
       </c>
       <c r="H3" t="n">
-        <v>130323000</v>
+        <v>148207000</v>
       </c>
       <c r="I3" t="n">
-        <v>148207000</v>
+        <v>65592000</v>
       </c>
       <c r="J3" t="n">
-        <v>-17884000</v>
+        <v>82615000</v>
       </c>
       <c r="K3" t="n">
-        <v>-203689000</v>
+        <v>-102114000</v>
       </c>
       <c r="L3" t="n">
-        <v>-15431000</v>
+        <v>10383000</v>
       </c>
       <c r="M3" t="n">
-        <v>-75676000</v>
+        <v>-39975000</v>
       </c>
       <c r="N3" t="n">
-        <v>-75676000</v>
+        <v>-39975000</v>
       </c>
       <c r="O3" t="n">
-        <v>-33081000</v>
+        <v>-6979000</v>
       </c>
       <c r="P3" t="n">
-        <v>-36400000</v>
+        <v>-14862000</v>
       </c>
       <c r="Q3" t="n">
-        <v>3319000</v>
+        <v>7883000</v>
       </c>
       <c r="R3" t="n">
-        <v>169000</v>
+        <v>-14997000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-14997000</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-15065000</v>
       </c>
       <c r="U3" t="n">
-        <v>221000</v>
+        <v>68000</v>
       </c>
       <c r="V3" t="n">
-        <v>169000</v>
+        <v>-14997000</v>
       </c>
       <c r="W3" t="n">
-        <v>-52000</v>
+        <v>-15065000</v>
       </c>
       <c r="X3" t="n">
-        <v>221000</v>
+        <v>68000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-59921000</v>
+        <v>-45197000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-655000</v>
+        <v>-5000000</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-655000</v>
+        <v>-5000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-22356000</v>
+        <v>-7838000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-22356000</v>
+        <v>-7838000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-36910000</v>
+        <v>-32359000</v>
       </c>
       <c r="AF3" t="n">
-        <v>426000</v>
+        <v>52669000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-37336000</v>
+        <v>-85028000</v>
       </c>
       <c r="AH3" t="n">
-        <v>245726000</v>
+        <v>229926000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-114903000</v>
+        <v>-68142000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17038000</v>
+        <v>9022000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-16677000</v>
+        <v>-18650000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-43829000</v>
+        <v>-53320000</v>
       </c>
       <c r="AM3" t="n">
-        <v>4445000</v>
+        <v>19491000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-12165000</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>-30382000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
       <c r="AP3" t="n">
-        <v>-36109000</v>
+        <v>-42429000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-4720000</v>
+        <v>6291000</v>
       </c>
       <c r="AR3" t="n">
-        <v>13952000</v>
+        <v>8721000</v>
       </c>
       <c r="AS3" t="n">
-        <v>70474000</v>
+        <v>68353000</v>
       </c>
       <c r="AT3" t="n">
-        <v>11631000</v>
+        <v>14921000</v>
       </c>
       <c r="AU3" t="n">
-        <v>70474000</v>
+        <v>68353000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-848000</v>
+        <v>-550000</v>
       </c>
       <c r="AW3" t="n">
-        <v>82000</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>280000</v>
+        <v>1479000</v>
       </c>
       <c r="AY3" t="n">
-        <v>324029000</v>
-      </c>
+        <v>269716000</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>137060000</v>
+        <v>186034000</v>
       </c>
       <c r="C4" t="n">
-        <v>-14862000</v>
+        <v>-36400000</v>
       </c>
       <c r="D4" t="n">
-        <v>-15065000</v>
+        <v>-52000</v>
       </c>
       <c r="E4" t="n">
-        <v>68000</v>
+        <v>221000</v>
       </c>
       <c r="F4" t="n">
-        <v>7883000</v>
+        <v>3319000</v>
       </c>
       <c r="G4" t="n">
-        <v>-92866000</v>
+        <v>-59692000</v>
       </c>
       <c r="H4" t="n">
+        <v>130323000</v>
+      </c>
+      <c r="I4" t="n">
         <v>148207000</v>
       </c>
-      <c r="I4" t="n">
-        <v>65592000</v>
-      </c>
       <c r="J4" t="n">
-        <v>82615000</v>
+        <v>-17884000</v>
       </c>
       <c r="K4" t="n">
-        <v>-102114000</v>
+        <v>-203689000</v>
       </c>
       <c r="L4" t="n">
-        <v>10383000</v>
+        <v>-15431000</v>
       </c>
       <c r="M4" t="n">
-        <v>-39975000</v>
+        <v>-75676000</v>
       </c>
       <c r="N4" t="n">
-        <v>-39975000</v>
+        <v>-75676000</v>
       </c>
       <c r="O4" t="n">
-        <v>-6979000</v>
+        <v>-33081000</v>
       </c>
       <c r="P4" t="n">
-        <v>-14862000</v>
+        <v>-36400000</v>
       </c>
       <c r="Q4" t="n">
-        <v>7883000</v>
+        <v>3319000</v>
       </c>
       <c r="R4" t="n">
-        <v>-14997000</v>
+        <v>169000</v>
       </c>
       <c r="S4" t="n">
-        <v>-14997000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-15065000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>68000</v>
+        <v>221000</v>
       </c>
       <c r="V4" t="n">
-        <v>-14997000</v>
+        <v>169000</v>
       </c>
       <c r="W4" t="n">
-        <v>-15065000</v>
+        <v>-52000</v>
       </c>
       <c r="X4" t="n">
-        <v>68000</v>
+        <v>221000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-45197000</v>
+        <v>-59921000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-5000000</v>
+        <v>-655000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-5000000</v>
+        <v>-655000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-7838000</v>
+        <v>-22356000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-7838000</v>
+        <v>-22356000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-32359000</v>
+        <v>-36910000</v>
       </c>
       <c r="AF4" t="n">
-        <v>52669000</v>
+        <v>426000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-85028000</v>
+        <v>-37336000</v>
       </c>
       <c r="AH4" t="n">
-        <v>229926000</v>
+        <v>245726000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-68142000</v>
+        <v>-114903000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>9022000</v>
+        <v>17038000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-18650000</v>
+        <v>-16677000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-53320000</v>
+        <v>-43829000</v>
       </c>
       <c r="AM4" t="n">
-        <v>19491000</v>
+        <v>4445000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-30382000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
+        <v>-12165000</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>-42429000</v>
+        <v>-36109000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6291000</v>
+        <v>-4720000</v>
       </c>
       <c r="AR4" t="n">
-        <v>8721000</v>
+        <v>13952000</v>
       </c>
       <c r="AS4" t="n">
-        <v>68353000</v>
+        <v>70474000</v>
       </c>
       <c r="AT4" t="n">
-        <v>14921000</v>
+        <v>11631000</v>
       </c>
       <c r="AU4" t="n">
-        <v>68353000</v>
+        <v>70474000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-550000</v>
+        <v>-848000</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>82000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1479000</v>
+        <v>280000</v>
       </c>
       <c r="AY4" t="n">
-        <v>269716000</v>
-      </c>
+        <v>324029000</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>7678000</v>
+        <v>249424000</v>
       </c>
       <c r="C5" t="n">
+        <v>-14949000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-102006000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>102176000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2942000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-106109000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>132194000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>130323000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1871000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-259807000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-123362000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-84674000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-84674000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-12007000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-14949000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2942000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>170000</v>
+      </c>
+      <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="n">
-        <v>-152079000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>122065000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1275000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-181859000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>65592000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>116803000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-51211000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-62286000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7352000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1275000</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1275000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-30014000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-30014000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-152079000</v>
-      </c>
       <c r="U5" t="n">
-        <v>122065000</v>
+        <v>102176000</v>
       </c>
       <c r="V5" t="n">
-        <v>-30014000</v>
+        <v>170000</v>
       </c>
       <c r="W5" t="n">
-        <v>-152079000</v>
+        <v>-102006000</v>
       </c>
       <c r="X5" t="n">
-        <v>122065000</v>
+        <v>102176000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-178462000</v>
+        <v>-93855000</v>
       </c>
       <c r="Z5" t="n">
-        <v>2640000</v>
+        <v>11891000</v>
       </c>
       <c r="AA5" t="n">
-        <v>19000000</v>
+        <v>12000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-16360000</v>
+        <v>-109000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3720000</v>
+        <v>-29407000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3720000</v>
+        <v>-29407000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-177973000</v>
+        <v>-76339000</v>
       </c>
       <c r="AF5" t="n">
-        <v>166000</v>
+        <v>363000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-178139000</v>
+        <v>-76702000</v>
       </c>
       <c r="AH5" t="n">
-        <v>189537000</v>
+        <v>355533000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-59978000</v>
+        <v>-109622000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4780000</v>
+        <v>17336000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-21185000</v>
+        <v>-17367000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-56693000</v>
+        <v>-4910000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-11762000</v>
+        <v>10669000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-39057000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1588000</v>
-      </c>
+        <v>-3641000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>-7462000</v>
+        <v>-11938000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12759000</v>
+        <v>-1992000</v>
       </c>
       <c r="AR5" t="n">
-        <v>10783000</v>
+        <v>11805000</v>
       </c>
       <c r="AS5" t="n">
-        <v>66707000</v>
+        <v>71092000</v>
       </c>
       <c r="AT5" t="n">
-        <v>16394000</v>
+        <v>9718000</v>
       </c>
       <c r="AU5" t="n">
-        <v>66707000</v>
+        <v>61374000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-210000</v>
+        <v>-551000</v>
       </c>
       <c r="AW5" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1632000</v>
+        <v>723000</v>
       </c>
       <c r="AY5" t="n">
-        <v>200664000</v>
+        <v>382019000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>127851000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-75713000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-117111000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>236971000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3346000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-302928000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>155976000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>132194000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23782000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-123690000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-128593000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-128593000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-72367000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-75713000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3346000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>119860000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>119860000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-117111000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>236971000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-283307000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-85000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-85000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-32599000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-32599000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-270021000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>308000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-270329000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>430779000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-114063000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>21226000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-16578000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-27522000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>7023000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-15231000</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>-19314000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-4847000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13391000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>81676000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10344000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>71332000</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>575000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>477381000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>19398000</v>
       </c>
     </row>
   </sheetData>
@@ -3847,197 +4053,197 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="EN1" t="inlineStr">
@@ -4062,10 +4268,8 @@
           <t>Cape Town</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>7550</t>
-        </is>
+      <c r="D2" t="n">
+        <v>7550</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4119,7 +4323,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Christian Phillipus David Vorster', 'age': 56, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 1883071, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ishak  Kula C.A.', 'title': 'CFO &amp; Executive Director', 'fiscalYear': 2025, 'totalPay': 321792, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jacobus Johannes Human', 'age': 60, 'title': 'Chief Operating Officer', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 632073, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Divya  Singh', 'age': 60, 'title': 'Chief Academic Officer &amp; Executive Director', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 664390, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Merwe  Roux', 'title': 'Group Chief Information Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Prof. Patrick  Bean', 'title': 'Executive Head of Contact Learning', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Andrew  Horsfall', 'title': 'Chief Executive Officer of Milpark Education', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Diaan  Lawrenson', 'title': 'Chief Executive Officer of AFDA', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Prof. Stanislaus Alexander du Plessis B.Com., Ph.D.', 'age': 52, 'title': 'Chief Executive Officer of Stadio Higher Education', 'yearBorn': 1973, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Christian Phillipus David Vorster', 'age': 56, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 1898617, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ishak  Kula C.A.', 'title': 'CFO &amp; Executive Director', 'fiscalYear': 2025, 'totalPay': 324449, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jacobus Johannes Human', 'age': 60, 'title': 'Chief Operating Officer', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 637291, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Divya  Singh', 'age': 60, 'title': 'Chief Academic Officer &amp; Executive Director', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 669875, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Merwe  Roux', 'title': 'Group Chief Information Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Prof. Patrick  Bean', 'title': 'Executive Head of Contact Learning', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Andrew  Horsfall', 'title': 'Chief Executive Officer of Milpark Education', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Diaan  Lawrenson', 'title': 'Chief Executive Officer of AFDA', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Prof. Stanislaus Alexander du Plessis B.Com., Ph.D.', 'age': 52, 'title': 'Chief Executive Officer of Stadio Higher Education', 'yearBorn': 1973, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4137,46 +4341,46 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>0.635</v>
+        <v>0.595</v>
       </c>
       <c r="U2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="V2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="W2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="X2" t="n">
-        <v>0.635</v>
+        <v>0.595</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="AB2" t="n">
         <v>0.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="AD2" t="n">
         <v>1776816000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4327</v>
+        <v>0.39740002</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="AG2" t="n">
-        <v>32.5</v>
+        <v>30.500002</v>
       </c>
       <c r="AH2" t="n">
         <v>520</v>
@@ -4194,16 +4398,16 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.63</v>
+        <v>0.625</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="AO2" t="n">
-        <v>551348416</v>
+        <v>517120000</v>
       </c>
       <c r="AP2" t="n">
-        <v>555399631</v>
+        <v>530805441</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.384</v>
@@ -4218,19 +4422,19 @@
         <v>0.0881</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.2994836</v>
+        <v>0.28089127</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.6022</v>
+        <v>0.6038</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.583195</v>
+        <v>0.59152</v>
       </c>
       <c r="AX2" t="n">
         <v>0.184</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.28976378</v>
+        <v>0.30924368</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
@@ -4241,31 +4445,31 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>715092928</v>
+        <v>668574656</v>
       </c>
       <c r="BC2" t="n">
         <v>0.17791</v>
       </c>
       <c r="BD2" t="n">
-        <v>586002830</v>
+        <v>595188066</v>
       </c>
       <c r="BE2" t="n">
-        <v>848228340</v>
+        <v>847737640</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.26173002</v>
+        <v>0.26189</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.30456</v>
+        <v>0.30735</v>
       </c>
       <c r="BH2" t="n">
-        <v>848228340</v>
+        <v>847737640</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.12958291</v>
+        <v>0.13074562</v>
       </c>
       <c r="BJ2" t="n">
-        <v>5.0160933</v>
+        <v>4.6655483</v>
       </c>
       <c r="BK2" t="n">
         <v>1767139200</v>
@@ -4286,16 +4490,16 @@
         <v>0.02</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.388</v>
+        <v>0.363</v>
       </c>
       <c r="BR2" t="n">
-        <v>1.423</v>
+        <v>1.331</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.49061036</v>
+        <v>0.51015234</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.2568333</v>
       </c>
       <c r="BU2" t="n">
         <v>0.184</v>
@@ -4309,7 +4513,7 @@
         </is>
       </c>
       <c r="BX2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -4412,145 +4616,145 @@
         </is>
       </c>
       <c r="DA2" t="n">
-        <v>0.066805005</v>
+        <v>2.5210059</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.11455004</v>
-      </c>
-      <c r="DC2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>finmb_537788354</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1756449000</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1742803200</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1742803200</v>
+      </c>
+      <c r="DM2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.0062000155</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.010268327</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.018480003</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.031241551</v>
+      </c>
+      <c r="DS2" t="n">
         <v>15</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DT2" t="n">
         <v>15</v>
       </c>
-      <c r="DE2" t="b">
+      <c r="DU2" t="b">
         <v>0</v>
       </c>
-      <c r="DF2" t="b">
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>1781849032</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>Stadio Holdings Ltd.          R</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>Stadio Holdings Limited</t>
+        </is>
+      </c>
+      <c r="EA2" t="b">
         <v>0</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="EB2" t="n">
         <v>1614668400000</v>
       </c>
-      <c r="DH2" t="n">
+      <c r="EC2" t="n">
         <v>0.014999986</v>
       </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>0.65 - 0.65</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>0.61 - 0.61</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
         <is>
           <t>Frankfurt</t>
         </is>
       </c>
-      <c r="DK2" t="n">
+      <c r="EF2" t="n">
         <v>0</v>
       </c>
-      <c r="DL2" t="n">
-        <v>0.26599997</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.69270825</v>
-      </c>
-      <c r="DN2" t="inlineStr">
+      <c r="EG2" t="n">
+        <v>0.22600001</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.5885416999999999</v>
+      </c>
+      <c r="EI2" t="inlineStr">
         <is>
           <t>0.384 - 0.705</t>
         </is>
       </c>
-      <c r="DO2" t="n">
-        <v>-0.055000007</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.07801419499999999</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>49.061035</v>
-      </c>
-      <c r="DR2" t="n">
+      <c r="EJ2" t="n">
+        <v>-0.09499997</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.13475174</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>51.015236</v>
+      </c>
+      <c r="EM2" t="n">
         <v>1756103400</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1756449000</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1742803200</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1742803200</v>
-      </c>
-      <c r="DV2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0.047800004</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.07937563</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>Stadio Holdings Limited</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>1780383947</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>finmb_537788354</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="EH2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>2.3622024</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>Stadio Holdings Ltd.          R</t>
-        </is>
       </c>
       <c r="EN2" t="inlineStr"/>
     </row>
